--- a/FINAL_SUBMISSION/07_交易决策记录/07_投资决策记录.xlsx
+++ b/FINAL_SUBMISSION/07_交易决策记录/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。指标信号：价；格；位；于；6；0；日；均；线；下；方；，；中；期；趋；势；偏；弱；；；R；S；I；=；2；7；.；0；超；卖；区</t>
+          <t>趋势中性，观望。指标信号：价格位于60日均线下方，中期趋势偏弱；RSI=27.0超卖区</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。指标信号：价；格；站；上；6；0；日；均；线；；；R；S；I；=；5；2；.；7；中；性；区</t>
+          <t>趋势中性，观望。指标信号：价格站上60日均线；RSI=52.7中性区</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。指标信号：均；线；多；头；排；列；(；5；&gt;；1；0；&gt;；2；0；&gt;；6；0；)；；；M；A；C；D；红；柱；放；大；；；R；S；I；=；8；4；.；9；超；买；区；，；短；期；回；调；风；险</t>
+          <t>中期趋势向上，可关注/持有。指标信号：均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.9超买区，短期回调风险</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -813,6 +813,366 @@
       <c r="R4" s="2" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>D2026090701</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>（510300）</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>258900</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1199743</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>综合评分55.5分（基本面60.0/技术面51.0）达标，目标仓位24%，买入后占比24.0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>跟踪宽基/行业指数，天然分散个股业绩风险；费用低、流动性好，适合作为组合底仓</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>趋势中性，观望。指标信号：价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.2超卖区</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>跟踪标的指数系统性下行风险；行业ETF受行业景气度波动影响较大</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比76%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D2026090702</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32.87</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>36500</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1199755</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>综合评分78.0分（基本面100/技术面56.0）达标，目标仓位24%，买入后占比24.0%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好；归母净利润同比+68.17%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>趋势中性，观望。指标信号：价格站上60日均线；RSI=48.3中性区</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比76%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>D2026090703</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>（601318）</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56.36</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>21200</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1194832</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>综合评分72.0分（基本面82.0/技术面62.0）达标，目标仓位24%，买入后占比23.9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好；归母净利润同比+36.06%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>中期趋势向上，可关注/持有。指标信号：均线多头排列(5&gt;10&gt;20&gt;60)；RSI=73.7中性区</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比76%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>D2026090801</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>（600900）</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27.87</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>376245</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>综合评分70.0分（基本面78.0/技术面62.0）达标，目标仓位24%，买入后占比7.5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长；归母净利润同比+13.02%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>中期趋势向上，可关注/持有。指标信号：均线多头排列(5&gt;10&gt;20&gt;60)；RSI=39.0中性区</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约9156亿元，较前5日均量放大（前5日均值约8871亿元），市场活跃度提升。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比20%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>

--- a/FINAL_SUBMISSION/07_交易决策记录/07_投资决策记录.xlsx
+++ b/FINAL_SUBMISSION/07_交易决策记录/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1172,7 +1172,97 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D20260909M01</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>33.86</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>616252</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>人工主动减仓：部分止盈，锁定收益。卖出 18200 股（占持仓 49.9%），成交价 33.860 元，相对成本 33.750 元实现盈利约 2002 元；剩余 18300 股继续持有。</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>基本面未出现恶化（加权ROE 19.60%、营收同比+15.78%、归母净利同比+68.17%），本次卖出属于价格与仓位纪律，不是基本面判断</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>中期趋势向上，可关注/持有。指标信号：价格站上60日均线；MACD红柱放大；RSI=59.4中性区（截至最近收盘；今日以限价 33.860 元成交）</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>沪深300 今日盘中 4564.42 点（+0.12%）；最近一次收盘观察（2026-09-08）：沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约9156亿元，较前5日均量放大（前5日均值约8871亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>锁定部分收益、降低单一标的集中度；卖出后仍持有 18300 股，组合现金占比回升，保留后续调仓能力</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比32%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>否（人工主动决策，系统当日未产生卖出信号）</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>人工判断，未采纳系统信号；系统仅提供行情、账本与规则校验支持</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘成交）</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
         </is>
       </c>
     </row>

--- a/FINAL_SUBMISSION/07_交易决策记录/07_投资决策记录.xlsx
+++ b/FINAL_SUBMISSION/07_交易决策记录/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额约9383亿元，较前5日均量放大（前5日均值约9168亿元），市场活跃度提升。；机会：当日领涨板块为畜禽饲料、生猪养殖、教育运营及其他，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额约20307亿元，较前5日均量放大（前5日均值约19632亿元），市场活跃度提升。；机会：当日领涨板块为畜禽饲料、生猪养殖、教育运营及其他，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额约9383亿元，较前5日均量放大（前5日均值约9168亿元），市场活跃度提升。；机会：当日领涨板块为畜禽饲料、生猪养殖、教育运营及其他，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额约20307亿元，较前5日均量放大（前5日均值约19632亿元），市场活跃度提升。；机会：当日领涨板块为畜禽饲料、生猪养殖、教育运营及其他，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额约9383亿元，较前5日均量放大（前5日均值约9168亿元），市场活跃度提升。；机会：当日领涨板块为畜禽饲料、生猪养殖、教育运营及其他，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额约20307亿元，较前5日均量放大（前5日均值约19632亿元），市场活跃度提升。；机会：当日领涨板块为畜禽饲料、生猪养殖、教育运营及其他，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约19460亿元，较前5日均量萎缩（前5日均值约19490亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约19460亿元，较前5日均量萎缩（前5日均值约19490亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约19460亿元，较前5日均量萎缩（前5日均值约19490亿元），市场情绪偏谨慎。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约9156亿元，较前5日均量放大（前5日均值约8871亿元），市场活跃度提升。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+          <t>沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约19603亿元，较前5日均量放大（前5日均值约19120亿元），市场活跃度提升。；机会：当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1184,83 +1184,443 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>D2026090901</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>34.40</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>16700</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>574480</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>综合评分80.0分（基本面100/技术面60.0）达标，目标仓位24%，买入后占比24.0%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好；归母净利润同比+68.17%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>中期趋势向上，可关注/持有。指标信号：价格站上60日均线；MACD红柱放大；RSI=54.0中性区</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4572.60点（+0.30%），跌破20日均线；两市成交额约18556亿元，较前5日均量萎缩（前5日均值约18974亿元），市场情绪偏谨慎。；机会：当日领涨板块为粮食种植、房产租赁经纪、磷肥及磷化工，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比21%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>D20260909M01</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>紫金矿业</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>（601899）</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>33.86</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>18200</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>616252</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>人工主动减仓：部分止盈，锁定收益。卖出 18200 股（占持仓 49.9%），成交价 33.860 元，相对成本 33.750 元实现盈利约 2002 元；剩余 18300 股继续持有。</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>基本面未出现恶化（加权ROE 19.60%、营收同比+15.78%、归母净利同比+68.17%），本次卖出属于价格与仓位纪律，不是基本面判断</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>中期趋势向上，可关注/持有。指标信号：价格站上60日均线；MACD红柱放大；RSI=59.4中性区（截至最近收盘；今日以限价 33.860 元成交）</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>沪深300 今日盘中 4564.42 点（+0.12%）；最近一次收盘观察（2026-09-08）：沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约9156亿元，较前5日均量放大（前5日均值约8871亿元），市场活跃度提升。</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>沪深300 今日盘中 4564.42 点（+0.12%）；最近一次收盘观察（2026-09-08）：沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约19603亿元，较前5日均量放大（前5日均值约19120亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>锁定部分收益、降低单一标的集中度；卖出后仍持有 18300 股，组合现金占比回升，保留后续调仓能力</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>规则引擎：GREEN；交易后现金占比32%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>否（人工主动决策，系统当日未产生卖出信号）</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>人工判断，未采纳系统信号；系统仅提供行情、账本与规则校验支持</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>CONFIRMED（人工主动决策，已于同花顺模拟盘成交）</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M01</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>新集能源</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>（601918）</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10.48</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>52400</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>人工主动建仓：煤炭板块低估值标的，买入 5000 股，成交价 10.480 元，金额 52,400 元（占组合约 1.0%）。</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>PE(TTM) 11.15、PB 1.49，处于煤炭板块估值低位；加权ROE 6.96%；营收同比 +35.82%、归母净利同比 +32.27%、毛利率 34.53%；煤电一体化经营，盈利与现金流相对稳定。</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>09-10 收 10.47 元（-0.38%）；价格站上 MA20(10.44) 与 MA60(9.78)；RSI=55.6 中性区（不超买）；近20日 +5.0%、近60日 +12.9%；距60日高点 -7.9%，仍有上行空间。</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>沪深300 收于 4548.39 点（-0.53%）；上证指数 3934.40（-0.43%）；深证成指 13617.67（-0.77%）；科创50 1569.22（-0.69%）。前一日（09-09）煤炭开采板块主力净流入 4.10 亿元、板块平均上涨 3.45%，贵金属 +9.02 亿元、工业金属 +8.86 亿元。</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>煤炭价格与下游需求波动风险；该标的**不在策略观察池(universe)内**，属人工扩展标的；本次建仓后组合现金占比降至约 8.5%，低于策略 20% 下限。</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比20%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>否（人工主动决策，系统当日未产生该标的买入信号）</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>人工判断，未采纳系统信号；系统仅提供行情、账本与规则校验支持</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘成交）</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M02</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>（600900）</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28.01</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>140050</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>人工主动加仓：原持仓 13500 股（成本 27.839 元），本次买入 5000 股，成交价 28.010 元，金额 140,050 元；加仓后持有 18500 股。</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>PE(TTM) 18.99、PB 3.18；加权ROE 6.55%；营收同比 +3.36%、归母净利同比 +13.02%、毛利率 57.89%；水电龙头，现金流稳定、分红确定性高，作为组合防御底仓。</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>09-10 收 28.09 元（+0.14%，逆势收红）；MA20=28.17、MA60=27.74，价格在 MA20 附近震荡、站上 MA60；RSI=52.9 中性区；近20日 -0.5%、近60日 +7.2%；距60日高点 -5.0%。</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>沪深300 收于 4548.39 点（-0.53%）；上证指数 3934.40（-0.43%）；深证成指 13617.67（-0.77%）；科创50 1569.22（-0.69%）。前一日（09-09）煤炭开采板块主力净流入 4.10 亿元、板块平均上涨 3.45%，贵金属 +9.02 亿元、工业金属 +8.86 亿元。</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>来水偏枯影响发电量；利率上行压制高股息资产估值；加仓后该标的占组合约 10.4%，仍在 30% 单只上限内。</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比17%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>否（人工主动决策，系统当日未产生该标的买入信号）</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>人工判断，未采纳系统信号；系统仅提供行情、账本与规则校验支持</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘成交）</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M03</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>美的集团</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>（000333）</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85.86</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>429305</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>人工主动建仓：分两笔成交，500 股 @85.870 元 + 4500 股 @85.860 元，合计 5000 股，加权均价 85.861 元，金额 429,305 元（占组合约 8.6%）。</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>PE(TTM) 14.82、PB 3.11；加权ROE 11.33%；营收同比 +3.46%、归母净利同比 +1.66%、毛利率 25.26%；白电龙头，全球化布局与ToB 业务提供增量。</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>09-10 收 86.20 元（+0.21%，逆势收红）；站上 MA20(85.79) 与 MA60(82.85)；RSI=60.3 中性偏强；近20日 +2.4%、近60日 +14.2%；距60日高点 -3.7%，接近突破。</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>沪深300 收于 4548.39 点（-0.53%）；上证指数 3934.40（-0.43%）；深证成指 13617.67（-0.77%）；科创50 1569.22（-0.69%）。前一日（09-09）煤炭开采板块主力净流入 4.10 亿元、板块平均上涨 3.45%，贵金属 +9.02 亿元、工业金属 +8.86 亿元。</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>家电内需与出口景气度波动；原材料（铜、铝）价格上涨挤压毛利；本次为新建仓，单只占比 8.6%，在 30% 上限内。</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比9%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>否（人工主动决策，系统当日未产生该标的买入信号）</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>人工判断，未采纳系统信号；系统仅提供行情、账本与规则校验支持</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘成交）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
